--- a/SECURITY_AUDIT_FINDINGS.xlsx
+++ b/SECURITY_AUDIT_FINDINGS.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -871,14 +871,14 @@
           <t>For buckets holding non-public content (resources, research, and review-gated uploads), set public=false and serve via signed URLs (createSignedUrl) or an authenticated read policy. Keep only genuinely public assets (e.g. avatars) public. Add upload content-type/size limits.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Open (risk-accepted)</t>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>DECISION 2026-07-06: full private-bucket + signed-URL refactor deferred (cross-cutting change to upload/render + data migration; not E2E-verifiable without prod risk). Residual risk reduced: URL-bearing DB rows are now authenticated-only (BUG-002/003), so file URLs are no longer exposed to anon. MITIGATION applied in security_hardening.sql (re-run to apply): file_size_limit + MIME allowlist on resources/research (25MB, docs+images), image-only 10MB on avatars/story-covers/event-posters/projects, 100MB size cap on showcase/community-media. FOLLOW-UP PLAN to fully close: (1) store object PATH not public URL in file_url/media_url; (2) createSignedUrl(path, ttl) at render server-side; (3) migrate existing rows path&lt;-parse(url); (4) alter buckets set public=false for resources+research; (5) test upload+open in-app.</t>
+          <t>COMPLETE fix for the sensitive member-content buckets. security_hardening.sql sets resources+research buckets private + adds member_content_read policy (authenticated); new lib/storage.ts converts stored public URLs/paths to short-lived SIGNED URLs; listResources (data layer) and research/[id] detail page render signed URLs (research edit still uses raw path). Display-asset buckets (avatars/story-covers/event-posters/showcase/projects/community-media) intentionally stay public with size/MIME limits (not sensitive). VERIFIED LIVE 2026-07-06 (headless): /resources Career category Open link is now https://.../object/SIGN/resources/...?token=... (scope=download, 1h exp); /resources+/profile render fine (design intact); tsc passes. Apply security_hardening.sql to flip buckets private; DEPLOY CODE FIRST.</t>
         </is>
       </c>
     </row>
@@ -979,64 +979,64 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>BUG-010</t>
+          <t>BUG-013</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Member email addresses over-fetched to all authenticated users (directory over-exposure)</t>
+          <t>Unsanitized user URLs on the event detail page (missed by BUG-006)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>API &amp; Client-Server Trust (over-fetching)</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>Input Validation &amp; Injection</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>supabase/setup_profiles_auth.sql:36-37 (profiles readable by all authenticated); directory/list queries selecting email</t>
+          <t>app/(app)/events/[id]/page.tsx:91,101,106 (recording_url, registration_link, online_link)</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Even after restricting anon access (BUG-002), the profiles policy lets ANY logged-in member read every other member's email column. A single logged-in account can scrape the entire membership's emails for spam/phishing. Email is not needed for the directory UI.</t>
+          <t>Same javascript:-URL stored/DOM XSS as BUG-006, on the event DETAIL page which the original BUG-006 fix missed (only EventsCalendar was patched). An admin/moderator setting an event's recording/registration/online link to 'javascript:...' runs script in an attendee's session when they click Watch/Register/Join.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Do not expose email in directory/listing reads. Either drop email from the SELECT column lists and RLS-visible surface for non-owners, or move email behind an owner/admin-only view or RPC. Show contact only via in-app messaging.</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Open (partially mitigated)</t>
+          <t>Wrap the three hrefs in safeUrl() (same helper as BUG-006).</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>MITIGATED 2026-07-06: lib/profiles.ts getFullProfile() now nulls `email` for anyone but the profile owner, so scholar/other-profile pages no longer ship member emails to the client (own email still comes from the auth session). tsc passes. RESIDUAL: a logged-in member can still hand-craft GET /rest/v1/profiles?select=email to scrape emails, because profiles_select grants row SELECT to authenticated and email lives on that table. FULL FIX (deferred - core-path risk): remove email from the profiles table read path (revoke column SELECT from anon/authenticated), refactor getFullProfile to select explicit columns instead of select('*'), and serve the owner's own email from auth.users. Anon scraping is already blocked by BUG-002.</t>
+          <t>Found during follow-up scan 2026-07-06. Applied safeUrl() to all 3 sinks + import; tsc passes. Identical pattern to the 10 BUG-006 sinks already validated by a passing production build. (Full build skipped intentionally to avoid corrupting the running dev server.)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>BUG-011</t>
+          <t>BUG-010</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Verbose authentication error messages returned to the client</t>
+          <t>Member email addresses over-fetched to all authenticated users (directory over-exposure)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Configuration &amp; Secrets (verbose errors)</t>
+          <t>API &amp; Client-Server Trust (over-fetching)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>app/login/actions.ts (login/signup return raw Supabase error.message)</t>
+          <t>supabase/setup_profiles_auth.sql:36-37 (profiles readable by all authenticated); directory/list queries selecting email</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Login and signup surface the raw Supabase error.message to the browser. Distinct messages (e.g. invalid credentials vs. unconfirmed email vs. rate-limited) can aid account enumeration and reconnaissance.</t>
+          <t>Even after restricting anon access (BUG-002), the profiles policy lets ANY logged-in member read every other member's email column. A single logged-in account can scrape the entire membership's emails for spam/phishing. Email is not needed for the directory UI.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Return a single generic message for auth failures (e.g. 'Invalid email or password.'). Log the detailed error server-side only. Keep distinct messaging only for non-sensitive validation (empty field).</t>
+          <t>Do not expose email in directory/listing reads. Either drop email from the SELECT column lists and RLS-visible surface for non-owners, or move email behind an owner/admin-only view or RPC. Show contact only via in-app messaging.</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -1066,54 +1066,148 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>app/login/actions.ts login(): auth failures now log the detailed Supabase error server-side and return a single generic 'Invalid email or password.', removing the invalid-user/unconfirmed/rate-limited oracle used for account enumeration. tsc passes. Signup's 'email already in use' left intact by design (standard signup UX, not a credential oracle).</t>
+          <t>COMPLETE fix. security_hardening.sql revokes table SELECT on public.profiles from anon+authenticated and grants column SELECT on all 22 columns EXCEPT email; lib/profiles.ts getFullProfile now selects explicit non-email columns (real schema pulled from live DB); Profile.email made optional. Admin email display unaffected (admin_* RPCs are SECURITY DEFINER); owner's own email comes from the auth session. VERIFIED 2026-07-06 (headless, dev): /profile and /resources render correctly =&gt; getFullProfile works with explicit select, design intact; tsc passes. DB revoke must be applied (security_hardening.sql) to block direct REST ?select=email; deploy code to prod before applying.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>BUG-011</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Verbose authentication error messages returned to the client</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Configuration &amp; Secrets (verbose errors)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>app/login/actions.ts (login/signup return raw Supabase error.message)</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Login and signup surface the raw Supabase error.message to the browser. Distinct messages (e.g. invalid credentials vs. unconfirmed email vs. rate-limited) can aid account enumeration and reconnaissance.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Return a single generic message for auth failures (e.g. 'Invalid email or password.'). Log the detailed error server-side only. Keep distinct messaging only for non-sensitive validation (empty field).</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>app/login/actions.ts login(): auth failures now log the detailed Supabase error server-side and return a single generic 'Invalid email or password.', removing the invalid-user/unconfirmed/rate-limited oracle used for account enumeration. tsc passes. Signup's 'email already in use' left intact by design (standard signup UX, not a credential oracle).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>BUG-012</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>get_enum_values() granted to anon (schema/enum information disclosure)</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>API &amp; Client-Server Trust</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>supabase/phase1_writes.sql:16-28 (grant get_enum_values to anon)</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>get_enum_values(text) is executable by anon and returns the labels of any enum type in the database, letting an unauthenticated caller enumerate internal enum definitions (roles, degree levels, etc.). Minor information disclosure that aids mapping the schema.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Restrict the grant to 'authenticated' only (revoke from anon). The dropdown-building use case is only needed after login.</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Repo: phase1_writes.sql revokes get_enum_values from public/anon, grants to authenticated only; applied live via security_hardening.sql. VERIFIED LIVE 2026-07-06: anon rpc/get_enum_values now returns HTTP 401 'permission denied for function' (baseline returned ['scholar','alumni','admin']). Regression re-sweep same session: profiles/alumni_details anon reads still [], default admin code still 401 — no earlier fix regressed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>BUG-014</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>@all mention broadcasts to all community members (notification spam)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Business Logic</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>supabase/phase29_community_interactions.sql (notify_community_mentions, @all branch)</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Any member who can post in a community may include '@all' to push a notification to every member of that community; it is not restricted to staff. Bounded to a single admin-curated community, so impact is minor notification spam rather than a platform-wide broadcast.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Optionally gate '@all' to community moderators/admins via community_can_moderate(), or accept as intended (comparable to Slack @channel).</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>notify_community_mentions @all branch now gated by community_can_moderate(p_community) (admin OR a manage_communities moderator who is a MEMBER of that community) instead of any platform moderator. Repo: phase29_community_interactions.sql + security_hardening.sql (round 2). CORRECTION: @all was already staff-gated (is_admin/mod_can); the round-1 'any member can @all' description was inaccurate. This tightens it to community scope per request. Apply security_hardening.sql.</t>
         </is>
       </c>
     </row>
